--- a/artfynd/A 71122-2021 artfynd.xlsx
+++ b/artfynd/A 71122-2021 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118376045</v>
+        <v>118376112</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594286</v>
+        <v>594278</v>
       </c>
       <c r="R3" t="n">
-        <v>6857219</v>
+        <v>6857215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376112</v>
+        <v>118376045</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594278</v>
+        <v>594286</v>
       </c>
       <c r="R4" t="n">
-        <v>6857215</v>
+        <v>6857219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 71122-2021 artfynd.xlsx
+++ b/artfynd/A 71122-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118374972</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118376112</v>
+        <v>118376045</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594278</v>
+        <v>594286</v>
       </c>
       <c r="R3" t="n">
-        <v>6857215</v>
+        <v>6857219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376045</v>
+        <v>118376112</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594286</v>
+        <v>594278</v>
       </c>
       <c r="R4" t="n">
-        <v>6857219</v>
+        <v>6857215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 71122-2021 artfynd.xlsx
+++ b/artfynd/A 71122-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118374972</v>
+        <v>118376112</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594284</v>
+        <v>594278</v>
       </c>
       <c r="R2" t="n">
-        <v>6857206</v>
+        <v>6857215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118376045</v>
+        <v>118374972</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594286</v>
+        <v>594284</v>
       </c>
       <c r="R3" t="n">
-        <v>6857219</v>
+        <v>6857206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376112</v>
+        <v>118376045</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594278</v>
+        <v>594286</v>
       </c>
       <c r="R4" t="n">
-        <v>6857215</v>
+        <v>6857219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 71122-2021 artfynd.xlsx
+++ b/artfynd/A 71122-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>119455159</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 71122-2021 artfynd.xlsx
+++ b/artfynd/A 71122-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>118374972</v>
       </c>
       <c r="B2" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,7 +715,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ol-Jons (Ol-Jons), Hls</t>
+          <t>Ol-Jons, Ol-Jons, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -789,12 +784,7 @@
         <v>118376045</v>
       </c>
       <c r="B3" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +821,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ol-Jons (Ol-Jons), Hls</t>
+          <t>Ol-Jons, Ol-Jons, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -900,12 +890,7 @@
         <v>118376112</v>
       </c>
       <c r="B4" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,7 +927,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ol-Jons (Ol-Jons), Hls</t>
+          <t>Ol-Jons, Ol-Jons, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1011,12 +996,7 @@
         <v>119455159</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
